--- a/docs/scrum/SIGRO - Sprint 1 · Tablero Scrum (tareas).xlsx
+++ b/docs/scrum/SIGRO - Sprint 1 · Tablero Scrum (tareas).xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas del tablero" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tablero'!$B$5:$L$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tablero'!$B$5:$L$266</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:K311"/>
+  <dimension ref="B2:K333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>T-004, T-006, T-234</t>
+          <t>T-004, T-006, T-240</t>
         </is>
       </c>
       <c r="J14" s="6" t="n"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>T-013, T-014, T-234</t>
+          <t>T-013, T-014, T-240</t>
         </is>
       </c>
       <c r="J24" s="6" t="n"/>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>T-030, T-031, T-234</t>
+          <t>T-030, T-031, T-240</t>
         </is>
       </c>
       <c r="J45" s="6" t="n"/>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>T-035, T-235</t>
+          <t>T-035, T-242</t>
         </is>
       </c>
       <c r="J55" s="6" t="n"/>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>T-057, T-235</t>
+          <t>T-057, T-242</t>
         </is>
       </c>
       <c r="J82" s="6" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>T-091, T-092, T-234</t>
+          <t>T-091, T-092, T-240</t>
         </is>
       </c>
       <c r="J122" s="6" t="n"/>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>T-099, T-100, T-234</t>
+          <t>T-099, T-100, T-240</t>
         </is>
       </c>
       <c r="J132" s="6" t="n"/>
@@ -5866,7 +5866,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>T-114, T-116, T-234</t>
+          <t>T-114, T-116, T-240</t>
         </is>
       </c>
       <c r="J152" s="6" t="n"/>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>T-123, T-124, T-234</t>
+          <t>T-123, T-124, T-240</t>
         </is>
       </c>
       <c r="J162" s="6" t="n"/>
@@ -6582,7 +6582,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>T-131, T-132, T-234</t>
+          <t>T-131, T-132, T-240</t>
         </is>
       </c>
       <c r="J172" s="6" t="n"/>
@@ -6940,7 +6940,7 @@
       </c>
       <c r="I182" s="6" t="inlineStr">
         <is>
-          <t>T-139, T-140, T-234</t>
+          <t>T-139, T-140, T-240</t>
         </is>
       </c>
       <c r="J182" s="6" t="n"/>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="I192" s="6" t="inlineStr">
         <is>
-          <t>T-147, T-148, T-234</t>
+          <t>T-147, T-148, T-240</t>
         </is>
       </c>
       <c r="J192" s="6" t="n"/>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="I202" s="6" t="inlineStr">
         <is>
-          <t>T-152, T-235</t>
+          <t>T-152, T-242</t>
         </is>
       </c>
       <c r="J202" s="6" t="n"/>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="I203" s="6" t="inlineStr">
         <is>
-          <t>T-155, T-156, T-234</t>
+          <t>T-155, T-156, T-240</t>
         </is>
       </c>
       <c r="J203" s="6" t="n"/>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="I211" s="6" t="inlineStr">
         <is>
-          <t>T-161, T-235</t>
+          <t>T-161, T-242</t>
         </is>
       </c>
       <c r="J211" s="6" t="n"/>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="I221" s="6" t="inlineStr">
         <is>
-          <t>T-167, T-235</t>
+          <t>T-167, T-242</t>
         </is>
       </c>
       <c r="J221" s="6" t="n"/>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="I231" s="6" t="inlineStr">
         <is>
-          <t>T-175, T-235</t>
+          <t>T-175, T-242</t>
         </is>
       </c>
       <c r="J231" s="6" t="n"/>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
-          <t>T-183, T-235</t>
+          <t>T-183, T-242</t>
         </is>
       </c>
       <c r="J242" s="6" t="n"/>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="I243" s="6" t="inlineStr">
         <is>
-          <t>T-186, T-188, T-234</t>
+          <t>T-186, T-188, T-240</t>
         </is>
       </c>
       <c r="J243" s="6" t="n"/>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="I253" s="6" t="inlineStr">
         <is>
-          <t>T-196, T-197, T-234</t>
+          <t>T-196, T-197, T-240</t>
         </is>
       </c>
       <c r="J253" s="6" t="n"/>
@@ -10204,7 +10204,7 @@
       </c>
       <c r="I273" s="6" t="inlineStr">
         <is>
-          <t>T-212, T-213, T-234</t>
+          <t>T-212, T-213, T-240</t>
         </is>
       </c>
       <c r="J273" s="6" t="n"/>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="I283" s="6" t="inlineStr">
         <is>
-          <t>T-217, T-235</t>
+          <t>T-217, T-242</t>
         </is>
       </c>
       <c r="J283" s="6" t="n"/>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="I293" s="6" t="inlineStr">
         <is>
-          <t>T-225, T-235</t>
+          <t>T-225, T-242</t>
         </is>
       </c>
       <c r="J293" s="6" t="n"/>
@@ -11017,7 +11017,7 @@
     <row r="296">
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tareas transversales (sin ellas ninguna HU llega a Done)   </t>
+          <t>HT-01 · Desplegar el ambiente de pruebas (historia técnica)   por votar</t>
         </is>
       </c>
     </row>
@@ -11064,103 +11064,68 @@
       </c>
     </row>
     <row r="298" ht="30" customHeight="1">
-      <c r="B298" s="6" t="inlineStr">
+      <c r="B298" s="8" t="inlineStr">
         <is>
           <t>T-234</t>
         </is>
       </c>
-      <c r="C298" s="7" t="inlineStr">
-        <is>
-          <t>Programar el ClienteHttp para que la web hable con la API real (snake_case ↔ camelCase, errores {codigo, mensaje})</t>
-        </is>
-      </c>
-      <c r="D298" s="6" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="E298" s="6" t="inlineStr">
-        <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="F298" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="G298" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H298" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="I298" s="6" t="n"/>
-      <c r="J298" s="6" t="n"/>
-      <c r="K298" s="7" t="inlineStr">
-        <is>
-          <t>desbloquea todas las tareas «Conectar…»</t>
-        </is>
-      </c>
-    </row>
-    <row r="299" ht="30" customHeight="1">
-      <c r="B299" s="6" t="inlineStr">
-        <is>
-          <t>T-235</t>
-        </is>
-      </c>
-      <c r="C299" s="7" t="inlineStr">
-        <is>
-          <t>Crear el proyecto base de la app: Compose, Room, WorkManager y cliente de la API</t>
-        </is>
-      </c>
-      <c r="D299" s="6" t="inlineStr">
-        <is>
-          <t>Android</t>
-        </is>
-      </c>
-      <c r="E299" s="6" t="inlineStr">
-        <is>
-          <t>Nicolás</t>
-        </is>
-      </c>
-      <c r="F299" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G299" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H299" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="I299" s="6" t="n"/>
-      <c r="J299" s="6" t="n"/>
-      <c r="K299" s="7" t="inlineStr">
-        <is>
-          <t>desbloquea todas las tareas Android</t>
+      <c r="C298" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-01 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D298" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E298" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F298" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G298" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H298" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I298" s="8" t="n"/>
+      <c r="J298" s="8" t="n"/>
+      <c r="K298" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>HT-02 · Configurar la integración continua (historia técnica)   por votar</t>
         </is>
       </c>
     </row>
     <row r="300" ht="30" customHeight="1">
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>T-236</t>
+          <t>T-235</t>
         </is>
       </c>
       <c r="C300" s="7" t="inlineStr">
         <is>
-          <t>Cargar en la base las semillas de los 626 proveedores reales</t>
+          <t>Configurar las pruebas automáticas en cada PR con GitHub Actions</t>
         </is>
       </c>
       <c r="D300" s="6" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="E300" s="6" t="inlineStr">
@@ -11169,7 +11134,7 @@
         </is>
       </c>
       <c r="F300" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G300" s="6" t="inlineStr">
         <is>
@@ -11178,111 +11143,80 @@
       </c>
       <c r="H300" s="6" t="inlineStr">
         <is>
-          <t>25/10</t>
+          <t>24/10</t>
         </is>
       </c>
       <c r="I300" s="6" t="n"/>
       <c r="J300" s="6" t="n"/>
-      <c r="K300" s="7" t="n"/>
+      <c r="K300" s="7" t="inlineStr">
+        <is>
+          <t>T5 de la DoD</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="30" customHeight="1">
-      <c r="B301" s="6" t="inlineStr">
-        <is>
-          <t>T-237</t>
-        </is>
-      </c>
-      <c r="C301" s="7" t="inlineStr">
-        <is>
-          <t>Configurar las pruebas automáticas en cada PR con GitHub Actions</t>
-        </is>
-      </c>
-      <c r="D301" s="6" t="inlineStr">
-        <is>
-          <t>DevOps</t>
-        </is>
-      </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="B301" s="8" t="inlineStr">
+        <is>
+          <t>T-236</t>
+        </is>
+      </c>
+      <c r="C301" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-02 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D301" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E301" s="8" t="inlineStr">
         <is>
           <t>Adiel</t>
         </is>
       </c>
-      <c r="F301" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G301" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H301" s="6" t="inlineStr">
-        <is>
-          <t>24/10</t>
-        </is>
-      </c>
-      <c r="I301" s="6" t="n"/>
-      <c r="J301" s="6" t="n"/>
-      <c r="K301" s="7" t="inlineStr">
-        <is>
-          <t>T5 de la DoD</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="30" customHeight="1">
-      <c r="B302" s="6" t="inlineStr">
-        <is>
-          <t>T-238</t>
-        </is>
-      </c>
-      <c r="C302" s="7" t="inlineStr">
-        <is>
-          <t>Poner el repositorio en privado e invitar al docente como lector</t>
-        </is>
-      </c>
-      <c r="D302" s="6" t="inlineStr">
-        <is>
-          <t>Scrum</t>
-        </is>
-      </c>
-      <c r="E302" s="6" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="F302" s="6" t="n">
+      <c r="F301" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="G302" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H302" s="6" t="inlineStr">
-        <is>
-          <t>23/10</t>
-        </is>
-      </c>
-      <c r="I302" s="6" t="n"/>
-      <c r="J302" s="6" t="n"/>
-      <c r="K302" s="7" t="inlineStr">
-        <is>
-          <t>hoy está público</t>
+      <c r="G301" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H301" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I301" s="8" t="n"/>
+      <c r="J301" s="8" t="n"/>
+      <c r="K301" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>HT-03 · Proteger el repositorio y main (historia técnica)   por votar</t>
         </is>
       </c>
     </row>
     <row r="303" ht="30" customHeight="1">
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>T-239</t>
+          <t>T-237</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>Armar el tablero en GitHub Projects con las plantillas de DoR y DoD</t>
+          <t>Poner el repositorio en privado e invitar al docente como lector</t>
         </is>
       </c>
       <c r="D303" s="6" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="E303" s="6" t="inlineStr">
@@ -11291,36 +11225,40 @@
         </is>
       </c>
       <c r="F303" s="6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G303" s="6" t="inlineStr">
         <is>
-          <t>Doing</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H303" s="6" t="inlineStr">
         <is>
-          <t>23/10</t>
+          <t>24/10</t>
         </is>
       </c>
       <c r="I303" s="6" t="n"/>
       <c r="J303" s="6" t="n"/>
-      <c r="K303" s="7" t="n"/>
+      <c r="K303" s="7" t="inlineStr">
+        <is>
+          <t>hoy está público</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="30" customHeight="1">
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>T-240</t>
+          <t>T-238</t>
         </is>
       </c>
       <c r="C304" s="7" t="inlineStr">
         <is>
-          <t>Facilitar el Daily Scrum de 15 minutos cada día, registrarlo y actualizar el burndown</t>
+          <t>Proteger la rama main: PR obligatorio con una aprobación de otro integrante</t>
         </is>
       </c>
       <c r="D304" s="6" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="E304" s="6" t="inlineStr">
@@ -11329,133 +11267,94 @@
         </is>
       </c>
       <c r="F304" s="6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G304" s="6" t="inlineStr">
         <is>
-          <t>Doing</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="H304" s="6" t="inlineStr">
         <is>
-          <t>27/10</t>
+          <t>24/10</t>
         </is>
       </c>
       <c r="I304" s="6" t="n"/>
       <c r="J304" s="6" t="n"/>
-      <c r="K304" s="7" t="inlineStr">
-        <is>
-          <t>hasta el 28/10</t>
-        </is>
-      </c>
+      <c r="K304" s="7" t="n"/>
     </row>
     <row r="305" ht="30" customHeight="1">
-      <c r="B305" s="6" t="inlineStr">
-        <is>
-          <t>T-241</t>
-        </is>
-      </c>
-      <c r="C305" s="7" t="inlineStr">
-        <is>
-          <t>Simplificar los textos de cada pantalla web: título y una línea, con ayuda «?» bajo demanda</t>
-        </is>
-      </c>
-      <c r="D305" s="6" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="E305" s="6" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="F305" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G305" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H305" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="I305" s="6" t="n"/>
-      <c r="J305" s="6" t="n"/>
-      <c r="K305" s="7" t="inlineStr">
-        <is>
-          <t>observación de Fernando: hoy hay demasiado texto</t>
-        </is>
-      </c>
-    </row>
-    <row r="306" ht="30" customHeight="1">
-      <c r="B306" s="6" t="inlineStr">
-        <is>
-          <t>T-242</t>
-        </is>
-      </c>
-      <c r="C306" s="7" t="inlineStr">
-        <is>
-          <t>Validar las pantallas con el cliente (Pool) en una sesión corta y registrar sus observaciones</t>
-        </is>
-      </c>
-      <c r="D306" s="6" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="E306" s="6" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="F306" s="6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G306" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H306" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="I306" s="6" t="n"/>
-      <c r="J306" s="6" t="n"/>
-      <c r="K306" s="7" t="inlineStr">
-        <is>
-          <t>que lo use quien lo va a usar</t>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>T-239</t>
+        </is>
+      </c>
+      <c r="C305" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-03 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D305" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E305" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F305" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G305" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H305" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I305" s="8" t="n"/>
+      <c r="J305" s="8" t="n"/>
+      <c r="K305" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>HT-04 · Conectar la web con la API real (historia técnica)   por votar</t>
         </is>
       </c>
     </row>
     <row r="307" ht="30" customHeight="1">
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>T-243</t>
+          <t>T-240</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>Revisar la app con guantes y al sol: botones grandes, una acción por pantalla, contraste AA</t>
+          <t>Programar el ClienteHttp para que la web hable con la API real (snake_case ↔ camelCase, errores {codigo, mensaje})</t>
         </is>
       </c>
       <c r="D307" s="6" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="E307" s="6" t="inlineStr">
         <is>
-          <t>Nicolás</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="F307" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G307" s="6" t="inlineStr">
         <is>
@@ -11471,108 +11370,73 @@
       <c r="J307" s="6" t="n"/>
       <c r="K307" s="7" t="inlineStr">
         <is>
-          <t>el almacenero trabaja en obra</t>
+          <t>desbloquea todas las tareas «Conectar…»</t>
         </is>
       </c>
     </row>
     <row r="308" ht="30" customHeight="1">
-      <c r="B308" s="6" t="inlineStr">
-        <is>
-          <t>T-244</t>
-        </is>
-      </c>
-      <c r="C308" s="7" t="inlineStr">
-        <is>
-          <t>Modelar los 3 diagramas de casos de uso y los 3 de secuencia (importación S10, salida sin señal, recepción y costo promedio)</t>
-        </is>
-      </c>
-      <c r="D308" s="6" t="inlineStr">
-        <is>
-          <t>Modelado UML</t>
-        </is>
-      </c>
-      <c r="E308" s="6" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="F308" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G308" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="H308" s="6" t="inlineStr">
-        <is>
-          <t>24/10</t>
-        </is>
-      </c>
-      <c r="I308" s="6" t="n"/>
-      <c r="J308" s="6" t="n"/>
-      <c r="K308" s="7" t="inlineStr">
-        <is>
-          <t>en el lienzo; cubren HU-07, 35, 37, 38, 40 y 55</t>
-        </is>
-      </c>
-    </row>
-    <row r="309" ht="30" customHeight="1">
-      <c r="B309" s="6" t="inlineStr">
-        <is>
-          <t>T-245</t>
-        </is>
-      </c>
-      <c r="C309" s="7" t="inlineStr">
-        <is>
-          <t>Dibujar los diagramas de actividades del negocio y de estados</t>
-        </is>
-      </c>
-      <c r="D309" s="6" t="inlineStr">
-        <is>
-          <t>Modelado UML</t>
-        </is>
-      </c>
-      <c r="E309" s="6" t="inlineStr">
-        <is>
-          <t>Nicolás</t>
-        </is>
-      </c>
-      <c r="F309" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G309" s="6" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="H309" s="6" t="inlineStr">
-        <is>
-          <t>24/10</t>
-        </is>
-      </c>
-      <c r="I309" s="6" t="n"/>
-      <c r="J309" s="6" t="n"/>
-      <c r="K309" s="7" t="inlineStr">
-        <is>
-          <t>14 hojas: A1–A4 y E1–E3 (22/10)</t>
+      <c r="B308" s="8" t="inlineStr">
+        <is>
+          <t>T-241</t>
+        </is>
+      </c>
+      <c r="C308" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-04 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D308" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E308" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F308" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G308" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H308" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I308" s="8" t="n"/>
+      <c r="J308" s="8" t="n"/>
+      <c r="K308" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>HT-05 · Crear la base de la app Android (historia técnica)   por votar</t>
         </is>
       </c>
     </row>
     <row r="310" ht="30" customHeight="1">
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>T-246</t>
+          <t>T-242</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
         <is>
-          <t>Dibujar la arquitectura en las cuatro vistas del C4 a partir del diagrama de microservicios</t>
+          <t>Crear el proyecto base de la app: Compose, Room, WorkManager y cliente de la API</t>
         </is>
       </c>
       <c r="D310" s="6" t="inlineStr">
         <is>
-          <t>Modelado UML</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="E310" s="6" t="inlineStr">
@@ -11581,7 +11445,7 @@
         </is>
       </c>
       <c r="F310" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G310" s="6" t="inlineStr">
         <is>
@@ -11590,62 +11454,831 @@
       </c>
       <c r="H310" s="6" t="inlineStr">
         <is>
-          <t>24/10</t>
+          <t>26/10</t>
         </is>
       </c>
       <c r="I310" s="6" t="n"/>
       <c r="J310" s="6" t="n"/>
       <c r="K310" s="7" t="inlineStr">
         <is>
+          <t>desbloquea todas las tareas Android</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="30" customHeight="1">
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>T-243</t>
+        </is>
+      </c>
+      <c r="C311" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-05 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F311" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G311" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I311" s="8" t="n"/>
+      <c r="J311" s="8" t="n"/>
+      <c r="K311" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>HT-06 · Publicar el contrato de la API y Postman (historia técnica)   por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="30" customHeight="1">
+      <c r="B313" s="6" t="inlineStr">
+        <is>
+          <t>T-244</t>
+        </is>
+      </c>
+      <c r="C313" s="7" t="inlineStr">
+        <is>
+          <t>Publicar el OpenAPI de la API en el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="D313" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E313" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F313" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" s="6" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+      <c r="H313" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="I313" s="6" t="n"/>
+      <c r="J313" s="6" t="n"/>
+      <c r="K313" s="7" t="inlineStr">
+        <is>
+          <t>Swagger de FastAPI ya existe en local</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="30" customHeight="1">
+      <c r="B314" s="6" t="inlineStr">
+        <is>
+          <t>T-245</t>
+        </is>
+      </c>
+      <c r="C314" s="7" t="inlineStr">
+        <is>
+          <t>Armar y compartir la colección de Postman con entorno de pruebas, login y un ejemplo correcto y uno de error por endpoint</t>
+        </is>
+      </c>
+      <c r="D314" s="6" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="E314" s="6" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="F314" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G314" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H314" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="I314" s="6" t="n"/>
+      <c r="J314" s="6" t="n"/>
+      <c r="K314" s="7" t="n"/>
+    </row>
+    <row r="315" ht="30" customHeight="1">
+      <c r="B315" s="8" t="inlineStr">
+        <is>
+          <t>T-246</t>
+        </is>
+      </c>
+      <c r="C315" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-06 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D315" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E315" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F315" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G315" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I315" s="8" t="n"/>
+      <c r="J315" s="8" t="n"/>
+      <c r="K315" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>HT-07 · Cargar los datos de prueba reales (historia técnica)   por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="30" customHeight="1">
+      <c r="B317" s="6" t="inlineStr">
+        <is>
+          <t>T-247</t>
+        </is>
+      </c>
+      <c r="C317" s="7" t="inlineStr">
+        <is>
+          <t>Cargar en la base los 626 proveedores y el catálogo de insumos del cliente</t>
+        </is>
+      </c>
+      <c r="D317" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E317" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F317" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H317" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="I317" s="6" t="n"/>
+      <c r="J317" s="6" t="n"/>
+      <c r="K317" s="7" t="inlineStr">
+        <is>
+          <t>cargador idempotente ya probado</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="30" customHeight="1">
+      <c r="B318" s="6" t="inlineStr">
+        <is>
+          <t>T-248</t>
+        </is>
+      </c>
+      <c r="C318" s="7" t="inlineStr">
+        <is>
+          <t>Crear la obra Multifamiliar Flores con su relación de insumos del S10 en la base de pruebas</t>
+        </is>
+      </c>
+      <c r="D318" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E318" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F318" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G318" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H318" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="I318" s="6" t="n"/>
+      <c r="J318" s="6" t="n"/>
+      <c r="K318" s="7" t="n"/>
+    </row>
+    <row r="319" ht="30" customHeight="1">
+      <c r="B319" s="8" t="inlineStr">
+        <is>
+          <t>T-249</t>
+        </is>
+      </c>
+      <c r="C319" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-07 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D319" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E319" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F319" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G319" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H319" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I319" s="8" t="n"/>
+      <c r="J319" s="8" t="n"/>
+      <c r="K319" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>HT-08 · Autenticar a los servicios entre sí (historia técnica)   por votar</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="30" customHeight="1">
+      <c r="B321" s="6" t="inlineStr">
+        <is>
+          <t>T-250</t>
+        </is>
+      </c>
+      <c r="C321" s="7" t="inlineStr">
+        <is>
+          <t>Exigir el token de servicio en Integraciones</t>
+        </is>
+      </c>
+      <c r="D321" s="6" t="inlineStr">
+        <is>
+          <t>Integración</t>
+        </is>
+      </c>
+      <c r="E321" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F321" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G321" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H321" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="I321" s="6" t="n"/>
+      <c r="J321" s="6" t="n"/>
+      <c r="K321" s="7" t="inlineStr">
+        <is>
+          <t>X-Servicio-Token, 22/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="30" customHeight="1">
+      <c r="B322" s="6" t="inlineStr">
+        <is>
+          <t>T-251</t>
+        </is>
+      </c>
+      <c r="C322" s="7" t="inlineStr">
+        <is>
+          <t>Configurar el token de servicio en docker compose y enviarlo desde la API a Integraciones y Notificaciones</t>
+        </is>
+      </c>
+      <c r="D322" s="6" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="E322" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F322" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G322" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H322" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="I322" s="6" t="n"/>
+      <c r="J322" s="6" t="n"/>
+      <c r="K322" s="7" t="n"/>
+    </row>
+    <row r="323" ht="30" customHeight="1">
+      <c r="B323" s="8" t="inlineStr">
+        <is>
+          <t>T-252</t>
+        </is>
+      </c>
+      <c r="C323" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-08 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="D323" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="E323" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="F323" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G323" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H323" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I323" s="8" t="n"/>
+      <c r="J323" s="8" t="n"/>
+      <c r="K323" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otras tareas transversales (Scrum, UX, diagramas, demo)   </t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="30" customHeight="1">
+      <c r="B325" s="6" t="inlineStr">
+        <is>
+          <t>T-253</t>
+        </is>
+      </c>
+      <c r="C325" s="7" t="inlineStr">
+        <is>
+          <t>Armar el tablero en GitHub Projects con las plantillas de DoR y DoD</t>
+        </is>
+      </c>
+      <c r="D325" s="6" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+      <c r="E325" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F325" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G325" s="6" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+      <c r="H325" s="6" t="inlineStr">
+        <is>
+          <t>23/10</t>
+        </is>
+      </c>
+      <c r="I325" s="6" t="n"/>
+      <c r="J325" s="6" t="n"/>
+      <c r="K325" s="7" t="n"/>
+    </row>
+    <row r="326" ht="30" customHeight="1">
+      <c r="B326" s="6" t="inlineStr">
+        <is>
+          <t>T-254</t>
+        </is>
+      </c>
+      <c r="C326" s="7" t="inlineStr">
+        <is>
+          <t>Facilitar el Daily Scrum de 15 minutos cada día, registrarlo y actualizar el burndown</t>
+        </is>
+      </c>
+      <c r="D326" s="6" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+      <c r="E326" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F326" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G326" s="6" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+      <c r="H326" s="6" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="I326" s="6" t="n"/>
+      <c r="J326" s="6" t="n"/>
+      <c r="K326" s="7" t="inlineStr">
+        <is>
+          <t>hasta el 28/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="30" customHeight="1">
+      <c r="B327" s="6" t="inlineStr">
+        <is>
+          <t>T-255</t>
+        </is>
+      </c>
+      <c r="C327" s="7" t="inlineStr">
+        <is>
+          <t>Simplificar los textos de cada pantalla web: título y una línea, con ayuda «?» bajo demanda</t>
+        </is>
+      </c>
+      <c r="D327" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E327" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F327" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G327" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H327" s="6" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="I327" s="6" t="n"/>
+      <c r="J327" s="6" t="n"/>
+      <c r="K327" s="7" t="inlineStr">
+        <is>
+          <t>observación de Fernando: hoy hay demasiado texto</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="30" customHeight="1">
+      <c r="B328" s="6" t="inlineStr">
+        <is>
+          <t>T-256</t>
+        </is>
+      </c>
+      <c r="C328" s="7" t="inlineStr">
+        <is>
+          <t>Validar las pantallas con el cliente (Pool) en una sesión corta y registrar sus observaciones</t>
+        </is>
+      </c>
+      <c r="D328" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E328" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F328" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G328" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H328" s="6" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="I328" s="6" t="n"/>
+      <c r="J328" s="6" t="n"/>
+      <c r="K328" s="7" t="inlineStr">
+        <is>
+          <t>que lo use quien lo va a usar</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="30" customHeight="1">
+      <c r="B329" s="6" t="inlineStr">
+        <is>
+          <t>T-257</t>
+        </is>
+      </c>
+      <c r="C329" s="7" t="inlineStr">
+        <is>
+          <t>Revisar la app con guantes y al sol: botones grandes, una acción por pantalla, contraste AA</t>
+        </is>
+      </c>
+      <c r="D329" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="E329" s="6" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="F329" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G329" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H329" s="6" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="I329" s="6" t="n"/>
+      <c r="J329" s="6" t="n"/>
+      <c r="K329" s="7" t="inlineStr">
+        <is>
+          <t>el almacenero trabaja en obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="330" ht="30" customHeight="1">
+      <c r="B330" s="6" t="inlineStr">
+        <is>
+          <t>T-258</t>
+        </is>
+      </c>
+      <c r="C330" s="7" t="inlineStr">
+        <is>
+          <t>Modelar los 3 diagramas de casos de uso y los 3 de secuencia (importación S10, salida sin señal, recepción y costo promedio)</t>
+        </is>
+      </c>
+      <c r="D330" s="6" t="inlineStr">
+        <is>
+          <t>Modelado UML</t>
+        </is>
+      </c>
+      <c r="E330" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="F330" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G330" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H330" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="I330" s="6" t="n"/>
+      <c r="J330" s="6" t="n"/>
+      <c r="K330" s="7" t="inlineStr">
+        <is>
+          <t>en el lienzo; cubren HU-07, 35, 37, 38, 40 y 55</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="30" customHeight="1">
+      <c r="B331" s="6" t="inlineStr">
+        <is>
+          <t>T-259</t>
+        </is>
+      </c>
+      <c r="C331" s="7" t="inlineStr">
+        <is>
+          <t>Dibujar los diagramas de actividades del negocio y de estados</t>
+        </is>
+      </c>
+      <c r="D331" s="6" t="inlineStr">
+        <is>
+          <t>Modelado UML</t>
+        </is>
+      </c>
+      <c r="E331" s="6" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="F331" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G331" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H331" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="I331" s="6" t="n"/>
+      <c r="J331" s="6" t="n"/>
+      <c r="K331" s="7" t="inlineStr">
+        <is>
+          <t>14 hojas: A1–A4 y E1–E3 (22/10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="30" customHeight="1">
+      <c r="B332" s="6" t="inlineStr">
+        <is>
+          <t>T-260</t>
+        </is>
+      </c>
+      <c r="C332" s="7" t="inlineStr">
+        <is>
+          <t>Dibujar la arquitectura en las cuatro vistas del C4 a partir del diagrama de microservicios</t>
+        </is>
+      </c>
+      <c r="D332" s="6" t="inlineStr">
+        <is>
+          <t>Modelado UML</t>
+        </is>
+      </c>
+      <c r="E332" s="6" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="F332" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G332" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H332" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="I332" s="6" t="n"/>
+      <c r="J332" s="6" t="n"/>
+      <c r="K332" s="7" t="inlineStr">
+        <is>
           <t>parte de api/docs/diagrama-microservicios.png</t>
         </is>
       </c>
     </row>
-    <row r="311" ht="30" customHeight="1">
-      <c r="B311" s="6" t="inlineStr">
-        <is>
-          <t>T-247</t>
-        </is>
-      </c>
-      <c r="C311" s="7" t="inlineStr">
+    <row r="333" ht="30" customHeight="1">
+      <c r="B333" s="6" t="inlineStr">
+        <is>
+          <t>T-261</t>
+        </is>
+      </c>
+      <c r="C333" s="7" t="inlineStr">
         <is>
           <t>Preparar la demo de la Sprint Review: una compra que cruza recepción, salida y costo de punta a punta</t>
         </is>
       </c>
-      <c r="D311" s="6" t="inlineStr">
+      <c r="D333" s="6" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="E333" s="6" t="inlineStr">
         <is>
           <t>Fernando</t>
         </is>
       </c>
-      <c r="F311" s="6" t="n">
+      <c r="F333" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G311" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="H311" s="6" t="inlineStr">
+      <c r="G333" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="H333" s="6" t="inlineStr">
         <is>
           <t>27/10</t>
         </is>
       </c>
-      <c r="I311" s="6" t="n"/>
-      <c r="J311" s="6" t="n"/>
-      <c r="K311" s="7" t="n"/>
+      <c r="I333" s="6" t="n"/>
+      <c r="J333" s="6" t="n"/>
+      <c r="K333" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="67">
     <mergeCell ref="B186:K186"/>
     <mergeCell ref="B257:K257"/>
     <mergeCell ref="B246:K246"/>
     <mergeCell ref="B49:K49"/>
     <mergeCell ref="B68:K68"/>
+    <mergeCell ref="B316:K316"/>
     <mergeCell ref="B6:K6"/>
     <mergeCell ref="B266:K266"/>
     <mergeCell ref="B256:K256"/>
@@ -11661,7 +12294,10 @@
     <mergeCell ref="B126:K126"/>
     <mergeCell ref="B106:K106"/>
     <mergeCell ref="B144:K144"/>
+    <mergeCell ref="B302:K302"/>
     <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B306:K306"/>
+    <mergeCell ref="B309:K309"/>
     <mergeCell ref="B224:K224"/>
     <mergeCell ref="B156:K156"/>
     <mergeCell ref="B125:K125"/>
@@ -11672,6 +12308,7 @@
     <mergeCell ref="B115:K115"/>
     <mergeCell ref="B155:K155"/>
     <mergeCell ref="B276:K276"/>
+    <mergeCell ref="B320:K320"/>
     <mergeCell ref="B214:K214"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B27:K27"/>
@@ -11680,6 +12317,7 @@
     <mergeCell ref="B105:K105"/>
     <mergeCell ref="B247:K247"/>
     <mergeCell ref="B176:K176"/>
+    <mergeCell ref="B324:K324"/>
     <mergeCell ref="B39:K39"/>
     <mergeCell ref="B77:K77"/>
     <mergeCell ref="B235:K235"/>
@@ -11691,6 +12329,8 @@
     <mergeCell ref="B287:K287"/>
     <mergeCell ref="B225:K225"/>
     <mergeCell ref="B145:K145"/>
+    <mergeCell ref="B299:K299"/>
+    <mergeCell ref="B312:K312"/>
     <mergeCell ref="B17:K17"/>
     <mergeCell ref="B175:K175"/>
     <mergeCell ref="B166:K166"/>
@@ -11701,7 +12341,7 @@
     <mergeCell ref="B196:K196"/>
     <mergeCell ref="B28:K28"/>
   </mergeCells>
-  <conditionalFormatting sqref="G6:G311">
+  <conditionalFormatting sqref="G6:G333">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$G6="Done"</formula>
     </cfRule>
@@ -11709,13 +12349,13 @@
       <formula>$G6="Doing"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J6:J311">
+  <conditionalFormatting sqref="J6:J333">
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>$J6="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J8 J9 J10 J11 J12 J13 J14 J15 J16 J19 J20 J21 J22 J23 J24 J25 J26 J29 J30 J31 J32 J33 J34 J35 J36 J37 J40 J41 J42 J43 J44 J45 J46 J47 J50 J51 J52 J53 J54 J55 J56 J57 J60 J61 J62 J63 J64 J65 J66 J69 J70 J71 J72 J73 J74 J75 J78 J79 J80 J81 J82 J83 J84 J85 J88 J89 J90 J91 J92 J93 J94 J95 J98 J99 J100 J101 J102 J103 J104 J107 J108 J109 J110 J111 J112 J113 J114 J117 J118 J119 J120 J121 J122 J123 J124 J127 J128 J129 J130 J131 J132 J133 J134 J137 J138 J139 J140 J141 J142 J143 J146 J147 J148 J149 J150 J151 J152 J153 J154 J157 J158 J159 J160 J161 J162 J163 J164 J167 J168 J169 J170 J171 J172 J173 J174 J177 J178 J179 J180 J181 J182 J183 J184 J187 J188 J189 J190 J191 J192 J193 J194 J197 J198 J199 J200 J201 J202 J203 J204 J205 J208 J209 J210 J211 J212 J213 J216 J217 J218 J219 J220 J221 J222 J223 J226 J227 J228 J229 J230 J231 J232 J233 J236 J237 J238 J239 J240 J241 J242 J243 J244 J245 J248 J249 J250 J251 J252 J253 J254 J255 J258 J259 J260 J261 J262 J263 J264 J265 J268 J269 J270 J271 J272 J273 J274 J275 J278 J279 J280 J281 J282 J283 J284 J285 J288 J289 J290 J291 J292 J293 J294 J295 J297 J298 J299 J300 J301 J302 J303 J304 J305 J306 J307 J308 J309 J310 J311" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J8 J9 J10 J11 J12 J13 J14 J15 J16 J19 J20 J21 J22 J23 J24 J25 J26 J29 J30 J31 J32 J33 J34 J35 J36 J37 J40 J41 J42 J43 J44 J45 J46 J47 J50 J51 J52 J53 J54 J55 J56 J57 J60 J61 J62 J63 J64 J65 J66 J69 J70 J71 J72 J73 J74 J75 J78 J79 J80 J81 J82 J83 J84 J85 J88 J89 J90 J91 J92 J93 J94 J95 J98 J99 J100 J101 J102 J103 J104 J107 J108 J109 J110 J111 J112 J113 J114 J117 J118 J119 J120 J121 J122 J123 J124 J127 J128 J129 J130 J131 J132 J133 J134 J137 J138 J139 J140 J141 J142 J143 J146 J147 J148 J149 J150 J151 J152 J153 J154 J157 J158 J159 J160 J161 J162 J163 J164 J167 J168 J169 J170 J171 J172 J173 J174 J177 J178 J179 J180 J181 J182 J183 J184 J187 J188 J189 J190 J191 J192 J193 J194 J197 J198 J199 J200 J201 J202 J203 J204 J205 J208 J209 J210 J211 J212 J213 J216 J217 J218 J219 J220 J221 J222 J223 J226 J227 J228 J229 J230 J231 J232 J233 J236 J237 J238 J239 J240 J241 J242 J243 J244 J245 J248 J249 J250 J251 J252 J253 J254 J255 J258 J259 J260 J261 J262 J263 J264 J265 J268 J269 J270 J271 J272 J273 J274 J275 J278 J279 J280 J281 J282 J283 J284 J285 J288 J289 J290 J291 J292 J293 J294 J295 J297 J298 J300 J301 J303 J304 J305 J307 J308 J310 J311 J313 J314 J315 J317 J318 J319 J321 J322 J323 J325 J326 J327 J328 J329 J330 J331 J332 J333" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11730,7 +12370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L252"/>
+  <dimension ref="B2:L266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -12171,7 +12811,7 @@
       <c r="K12" s="7" t="inlineStr"/>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>T-004, T-006, T-234</t>
+          <t>T-004, T-006, T-240</t>
         </is>
       </c>
     </row>
@@ -12587,7 +13227,7 @@
       <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>T-013, T-014, T-234</t>
+          <t>T-013, T-014, T-240</t>
         </is>
       </c>
     </row>
@@ -13474,7 +14114,7 @@
       <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>T-030, T-031, T-234</t>
+          <t>T-030, T-031, T-240</t>
         </is>
       </c>
     </row>
@@ -13890,7 +14530,7 @@
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>T-035, T-235</t>
+          <t>T-035, T-242</t>
         </is>
       </c>
     </row>
@@ -14985,7 +15625,7 @@
       <c r="K66" s="7" t="inlineStr"/>
       <c r="L66" s="7" t="inlineStr">
         <is>
-          <t>T-057, T-235</t>
+          <t>T-057, T-242</t>
         </is>
       </c>
     </row>
@@ -16657,7 +17297,7 @@
       <c r="K98" s="7" t="inlineStr"/>
       <c r="L98" s="7" t="inlineStr">
         <is>
-          <t>T-091, T-092, T-234</t>
+          <t>T-091, T-092, T-240</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17713,7 @@
       <c r="K106" s="7" t="inlineStr"/>
       <c r="L106" s="7" t="inlineStr">
         <is>
-          <t>T-099, T-100, T-234</t>
+          <t>T-099, T-100, T-240</t>
         </is>
       </c>
     </row>
@@ -17905,7 +18545,7 @@
       <c r="K122" s="7" t="inlineStr"/>
       <c r="L122" s="7" t="inlineStr">
         <is>
-          <t>T-114, T-116, T-234</t>
+          <t>T-114, T-116, T-240</t>
         </is>
       </c>
     </row>
@@ -18321,7 +18961,7 @@
       <c r="K130" s="7" t="inlineStr"/>
       <c r="L130" s="7" t="inlineStr">
         <is>
-          <t>T-123, T-124, T-234</t>
+          <t>T-123, T-124, T-240</t>
         </is>
       </c>
     </row>
@@ -18737,7 +19377,7 @@
       <c r="K138" s="7" t="inlineStr"/>
       <c r="L138" s="7" t="inlineStr">
         <is>
-          <t>T-131, T-132, T-234</t>
+          <t>T-131, T-132, T-240</t>
         </is>
       </c>
     </row>
@@ -19153,7 +19793,7 @@
       <c r="K146" s="7" t="inlineStr"/>
       <c r="L146" s="7" t="inlineStr">
         <is>
-          <t>T-139, T-140, T-234</t>
+          <t>T-139, T-140, T-240</t>
         </is>
       </c>
     </row>
@@ -19569,7 +20209,7 @@
       <c r="K154" s="7" t="inlineStr"/>
       <c r="L154" s="7" t="inlineStr">
         <is>
-          <t>T-147, T-148, T-234</t>
+          <t>T-147, T-148, T-240</t>
         </is>
       </c>
     </row>
@@ -19985,7 +20625,7 @@
       <c r="K162" s="7" t="inlineStr"/>
       <c r="L162" s="7" t="inlineStr">
         <is>
-          <t>T-152, T-235</t>
+          <t>T-152, T-242</t>
         </is>
       </c>
     </row>
@@ -20036,7 +20676,7 @@
       <c r="K163" s="7" t="inlineStr"/>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>T-155, T-156, T-234</t>
+          <t>T-155, T-156, T-240</t>
         </is>
       </c>
     </row>
@@ -20350,7 +20990,7 @@
       <c r="K169" s="7" t="inlineStr"/>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>T-161, T-235</t>
+          <t>T-161, T-242</t>
         </is>
       </c>
     </row>
@@ -20766,7 +21406,7 @@
       <c r="K177" s="7" t="inlineStr"/>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>T-167, T-235</t>
+          <t>T-167, T-242</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21822,7 @@
       <c r="K185" s="7" t="inlineStr"/>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>T-175, T-235</t>
+          <t>T-175, T-242</t>
         </is>
       </c>
     </row>
@@ -21649,7 +22289,7 @@
       <c r="K194" s="7" t="inlineStr"/>
       <c r="L194" s="7" t="inlineStr">
         <is>
-          <t>T-183, T-235</t>
+          <t>T-183, T-242</t>
         </is>
       </c>
     </row>
@@ -21700,7 +22340,7 @@
       <c r="K195" s="7" t="inlineStr"/>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>T-186, T-188, T-234</t>
+          <t>T-186, T-188, T-240</t>
         </is>
       </c>
     </row>
@@ -22116,7 +22756,7 @@
       <c r="K203" s="7" t="inlineStr"/>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>T-196, T-197, T-234</t>
+          <t>T-196, T-197, T-240</t>
         </is>
       </c>
     </row>
@@ -22948,7 +23588,7 @@
       <c r="K219" s="7" t="inlineStr"/>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>T-212, T-213, T-234</t>
+          <t>T-212, T-213, T-240</t>
         </is>
       </c>
     </row>
@@ -23364,7 +24004,7 @@
       <c r="K227" s="7" t="inlineStr"/>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>T-217, T-235</t>
+          <t>T-217, T-242</t>
         </is>
       </c>
     </row>
@@ -23776,7 +24416,7 @@
       <c r="K235" s="7" t="inlineStr"/>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>T-225, T-235</t>
+          <t>T-225, T-242</t>
         </is>
       </c>
     </row>
@@ -23898,12 +24538,12 @@
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-01</t>
         </is>
       </c>
       <c r="D238" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Desplegar el ambiente de pruebas</t>
         </is>
       </c>
       <c r="E238" s="6" t="inlineStr">
@@ -23942,55 +24582,55 @@
       <c r="L238" s="7" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="B239" s="6" t="inlineStr">
+      <c r="B239" s="8" t="inlineStr">
         <is>
           <t>T-234</t>
         </is>
       </c>
-      <c r="C239" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D239" s="7" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E239" s="6" t="inlineStr">
-        <is>
-          <t>Web</t>
-        </is>
-      </c>
-      <c r="F239" s="7" t="inlineStr">
-        <is>
-          <t>Programar el ClienteHttp para que la web hable con la API real (snake_case ↔ camelCase, errores {codigo, mensaje})</t>
-        </is>
-      </c>
-      <c r="G239" s="6" t="inlineStr">
-        <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="H239" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I239" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="J239" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="K239" s="7" t="inlineStr">
-        <is>
-          <t>desbloquea todas las tareas «Conectar…»</t>
-        </is>
-      </c>
-      <c r="L239" s="7" t="inlineStr"/>
+      <c r="C239" s="8" t="inlineStr">
+        <is>
+          <t>HT-01</t>
+        </is>
+      </c>
+      <c r="D239" s="9" t="inlineStr">
+        <is>
+          <t>Desplegar el ambiente de pruebas</t>
+        </is>
+      </c>
+      <c r="E239" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F239" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-01 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G239" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H239" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I239" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J239" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K239" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L239" s="9" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="B240" s="6" t="inlineStr">
@@ -24000,31 +24640,31 @@
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-02</t>
         </is>
       </c>
       <c r="D240" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Configurar la integración continua</t>
         </is>
       </c>
       <c r="E240" s="6" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>Crear el proyecto base de la app: Compose, Room, WorkManager y cliente de la API</t>
+          <t>Configurar las pruebas automáticas en cada PR con GitHub Actions</t>
         </is>
       </c>
       <c r="G240" s="6" t="inlineStr">
         <is>
-          <t>Nicolás</t>
+          <t>Adiel</t>
         </is>
       </c>
       <c r="H240" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I240" s="6" t="inlineStr">
         <is>
@@ -24033,62 +24673,66 @@
       </c>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>26/10</t>
+          <t>24/10</t>
         </is>
       </c>
       <c r="K240" s="7" t="inlineStr">
         <is>
-          <t>desbloquea todas las tareas Android</t>
+          <t>T5 de la DoD</t>
         </is>
       </c>
       <c r="L240" s="7" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="B241" s="6" t="inlineStr">
+      <c r="B241" s="8" t="inlineStr">
         <is>
           <t>T-236</t>
         </is>
       </c>
-      <c r="C241" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D241" s="7" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E241" s="6" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="F241" s="7" t="inlineStr">
-        <is>
-          <t>Cargar en la base las semillas de los 626 proveedores reales</t>
-        </is>
-      </c>
-      <c r="G241" s="6" t="inlineStr">
+      <c r="C241" s="8" t="inlineStr">
+        <is>
+          <t>HT-02</t>
+        </is>
+      </c>
+      <c r="D241" s="9" t="inlineStr">
+        <is>
+          <t>Configurar la integración continua</t>
+        </is>
+      </c>
+      <c r="E241" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F241" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-02 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G241" s="8" t="inlineStr">
         <is>
           <t>Adiel</t>
         </is>
       </c>
-      <c r="H241" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I241" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="J241" s="6" t="inlineStr">
-        <is>
-          <t>25/10</t>
-        </is>
-      </c>
-      <c r="K241" s="7" t="inlineStr"/>
-      <c r="L241" s="7" t="inlineStr"/>
+      <c r="H241" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I241" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J241" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K241" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L241" s="9" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="B242" s="6" t="inlineStr">
@@ -24098,12 +24742,12 @@
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-03</t>
         </is>
       </c>
       <c r="D242" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Proteger el repositorio y main</t>
         </is>
       </c>
       <c r="E242" s="6" t="inlineStr">
@@ -24113,16 +24757,16 @@
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>Configurar las pruebas automáticas en cada PR con GitHub Actions</t>
+          <t>Poner el repositorio en privado e invitar al docente como lector</t>
         </is>
       </c>
       <c r="G242" s="6" t="inlineStr">
         <is>
-          <t>Adiel</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="H242" s="6" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="I242" s="6" t="inlineStr">
         <is>
@@ -24136,7 +24780,7 @@
       </c>
       <c r="K242" s="7" t="inlineStr">
         <is>
-          <t>T5 de la DoD</t>
+          <t>hoy está público</t>
         </is>
       </c>
       <c r="L242" s="7" t="inlineStr"/>
@@ -24149,22 +24793,22 @@
       </c>
       <c r="C243" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-03</t>
         </is>
       </c>
       <c r="D243" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Proteger el repositorio y main</t>
         </is>
       </c>
       <c r="E243" s="6" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>DevOps</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>Poner el repositorio en privado e invitar al docente como lector</t>
+          <t>Proteger la rama main: PR obligatorio con una aprobación de otro integrante</t>
         </is>
       </c>
       <c r="G243" s="6" t="inlineStr">
@@ -24182,62 +24826,62 @@
       </c>
       <c r="J243" s="6" t="inlineStr">
         <is>
-          <t>23/10</t>
-        </is>
-      </c>
-      <c r="K243" s="7" t="inlineStr">
-        <is>
-          <t>hoy está público</t>
-        </is>
-      </c>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="K243" s="7" t="inlineStr"/>
       <c r="L243" s="7" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="B244" s="6" t="inlineStr">
+      <c r="B244" s="8" t="inlineStr">
         <is>
           <t>T-239</t>
         </is>
       </c>
-      <c r="C244" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D244" s="7" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E244" s="6" t="inlineStr">
-        <is>
-          <t>Scrum</t>
-        </is>
-      </c>
-      <c r="F244" s="7" t="inlineStr">
-        <is>
-          <t>Armar el tablero en GitHub Projects con las plantillas de DoR y DoD</t>
-        </is>
-      </c>
-      <c r="G244" s="6" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="H244" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I244" s="6" t="inlineStr">
-        <is>
-          <t>Doing</t>
-        </is>
-      </c>
-      <c r="J244" s="6" t="inlineStr">
-        <is>
-          <t>23/10</t>
-        </is>
-      </c>
-      <c r="K244" s="7" t="inlineStr"/>
-      <c r="L244" s="7" t="inlineStr"/>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>HT-03</t>
+        </is>
+      </c>
+      <c r="D244" s="9" t="inlineStr">
+        <is>
+          <t>Proteger el repositorio y main</t>
+        </is>
+      </c>
+      <c r="E244" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F244" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-03 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G244" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H244" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I244" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J244" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K244" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L244" s="9" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="B245" s="6" t="inlineStr">
@@ -24247,99 +24891,99 @@
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-04</t>
         </is>
       </c>
       <c r="D245" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Conectar la web con la API real</t>
         </is>
       </c>
       <c r="E245" s="6" t="inlineStr">
         <is>
-          <t>Scrum</t>
+          <t>Web</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>Facilitar el Daily Scrum de 15 minutos cada día, registrarlo y actualizar el burndown</t>
+          <t>Programar el ClienteHttp para que la web hable con la API real (snake_case ↔ camelCase, errores {codigo, mensaje})</t>
         </is>
       </c>
       <c r="G245" s="6" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="H245" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I245" s="6" t="inlineStr">
         <is>
-          <t>Doing</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="J245" s="6" t="inlineStr">
         <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="K245" s="7" t="inlineStr">
+        <is>
+          <t>desbloquea todas las tareas «Conectar…»</t>
+        </is>
+      </c>
+      <c r="L245" s="7" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>T-241</t>
+        </is>
+      </c>
+      <c r="C246" s="8" t="inlineStr">
+        <is>
+          <t>HT-04</t>
+        </is>
+      </c>
+      <c r="D246" s="9" t="inlineStr">
+        <is>
+          <t>Conectar la web con la API real</t>
+        </is>
+      </c>
+      <c r="E246" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F246" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-04 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G246" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H246" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I246" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J246" s="8" t="inlineStr">
+        <is>
           <t>27/10</t>
         </is>
       </c>
-      <c r="K245" s="7" t="inlineStr">
-        <is>
-          <t>hasta el 28/10</t>
-        </is>
-      </c>
-      <c r="L245" s="7" t="inlineStr"/>
-    </row>
-    <row r="246">
-      <c r="B246" s="6" t="inlineStr">
-        <is>
-          <t>T-241</t>
-        </is>
-      </c>
-      <c r="C246" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D246" s="7" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E246" s="6" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="F246" s="7" t="inlineStr">
-        <is>
-          <t>Simplificar los textos de cada pantalla web: título y una línea, con ayuda «?» bajo demanda</t>
-        </is>
-      </c>
-      <c r="G246" s="6" t="inlineStr">
-        <is>
-          <t>Fernando</t>
-        </is>
-      </c>
-      <c r="H246" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I246" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="J246" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="K246" s="7" t="inlineStr">
-        <is>
-          <t>observación de Fernando: hoy hay demasiado texto</t>
-        </is>
-      </c>
-      <c r="L246" s="7" t="inlineStr"/>
+      <c r="K246" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L246" s="9" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="B247" s="6" t="inlineStr">
@@ -24349,31 +24993,31 @@
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-05</t>
         </is>
       </c>
       <c r="D247" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Crear la base de la app Android</t>
         </is>
       </c>
       <c r="E247" s="6" t="inlineStr">
         <is>
-          <t>UX</t>
+          <t>Android</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
         <is>
-          <t>Validar las pantallas con el cliente (Pool) en una sesión corta y registrar sus observaciones</t>
+          <t>Crear el proyecto base de la app: Compose, Room, WorkManager y cliente de la API</t>
         </is>
       </c>
       <c r="G247" s="6" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Nicolás</t>
         </is>
       </c>
       <c r="H247" s="6" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="I247" s="6" t="inlineStr">
         <is>
@@ -24387,61 +25031,61 @@
       </c>
       <c r="K247" s="7" t="inlineStr">
         <is>
-          <t>que lo use quien lo va a usar</t>
+          <t>desbloquea todas las tareas Android</t>
         </is>
       </c>
       <c r="L247" s="7" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="B248" s="6" t="inlineStr">
+      <c r="B248" s="8" t="inlineStr">
         <is>
           <t>T-243</t>
         </is>
       </c>
-      <c r="C248" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D248" s="7" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E248" s="6" t="inlineStr">
-        <is>
-          <t>UX</t>
-        </is>
-      </c>
-      <c r="F248" s="7" t="inlineStr">
-        <is>
-          <t>Revisar la app con guantes y al sol: botones grandes, una acción por pantalla, contraste AA</t>
-        </is>
-      </c>
-      <c r="G248" s="6" t="inlineStr">
-        <is>
-          <t>Nicolás</t>
-        </is>
-      </c>
-      <c r="H248" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="I248" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="J248" s="6" t="inlineStr">
-        <is>
-          <t>26/10</t>
-        </is>
-      </c>
-      <c r="K248" s="7" t="inlineStr">
-        <is>
-          <t>el almacenero trabaja en obra</t>
-        </is>
-      </c>
-      <c r="L248" s="7" t="inlineStr"/>
+      <c r="C248" s="8" t="inlineStr">
+        <is>
+          <t>HT-05</t>
+        </is>
+      </c>
+      <c r="D248" s="9" t="inlineStr">
+        <is>
+          <t>Crear la base de la app Android</t>
+        </is>
+      </c>
+      <c r="E248" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-05 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G248" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H248" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I248" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J248" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K248" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L248" s="9" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="B249" s="6" t="inlineStr">
@@ -24451,45 +25095,45 @@
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-06</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Publicar el contrato de la API y Postman</t>
         </is>
       </c>
       <c r="E249" s="6" t="inlineStr">
         <is>
-          <t>Modelado UML</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
-          <t>Modelar los 3 diagramas de casos de uso y los 3 de secuencia (importación S10, salida sin señal, recepción y costo promedio)</t>
+          <t>Publicar el OpenAPI de la API en el ambiente de pruebas</t>
         </is>
       </c>
       <c r="G249" s="6" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Adiel</t>
         </is>
       </c>
       <c r="H249" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I249" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Doing</t>
         </is>
       </c>
       <c r="J249" s="6" t="inlineStr">
         <is>
-          <t>24/10</t>
+          <t>25/10</t>
         </is>
       </c>
       <c r="K249" s="7" t="inlineStr">
         <is>
-          <t>en el lienzo; cubren HU-07, 35, 37, 38, 40 y 55</t>
+          <t>Swagger de FastAPI ya existe en local</t>
         </is>
       </c>
       <c r="L249" s="7" t="inlineStr"/>
@@ -24502,35 +25146,35 @@
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HT-06</t>
         </is>
       </c>
       <c r="D250" s="7" t="inlineStr">
         <is>
-          <t>Transversal</t>
+          <t>Publicar el contrato de la API y Postman</t>
         </is>
       </c>
       <c r="E250" s="6" t="inlineStr">
         <is>
-          <t>Modelado UML</t>
+          <t>Pruebas</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
-          <t>Dibujar los diagramas de actividades del negocio y de estados</t>
+          <t>Armar y compartir la colección de Postman con entorno de pruebas, login y un ejemplo correcto y uno de error por endpoint</t>
         </is>
       </c>
       <c r="G250" s="6" t="inlineStr">
         <is>
-          <t>Nicolás</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="H250" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I250" s="6" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>To Do</t>
         </is>
       </c>
       <c r="J250" s="6" t="inlineStr">
@@ -24538,63 +25182,59 @@
           <t>24/10</t>
         </is>
       </c>
-      <c r="K250" s="7" t="inlineStr">
-        <is>
-          <t>14 hojas: A1–A4 y E1–E3 (22/10)</t>
-        </is>
-      </c>
+      <c r="K250" s="7" t="inlineStr"/>
       <c r="L250" s="7" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="B251" s="6" t="inlineStr">
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>T-246</t>
         </is>
       </c>
-      <c r="C251" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D251" s="7" t="inlineStr">
-        <is>
-          <t>Transversal</t>
-        </is>
-      </c>
-      <c r="E251" s="6" t="inlineStr">
-        <is>
-          <t>Modelado UML</t>
-        </is>
-      </c>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>Dibujar la arquitectura en las cuatro vistas del C4 a partir del diagrama de microservicios</t>
-        </is>
-      </c>
-      <c r="G251" s="6" t="inlineStr">
-        <is>
-          <t>Nicolás</t>
-        </is>
-      </c>
-      <c r="H251" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="I251" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="J251" s="6" t="inlineStr">
-        <is>
-          <t>24/10</t>
-        </is>
-      </c>
-      <c r="K251" s="7" t="inlineStr">
-        <is>
-          <t>parte de api/docs/diagrama-microservicios.png</t>
-        </is>
-      </c>
-      <c r="L251" s="7" t="inlineStr"/>
+      <c r="C251" s="8" t="inlineStr">
+        <is>
+          <t>HT-06</t>
+        </is>
+      </c>
+      <c r="D251" s="9" t="inlineStr">
+        <is>
+          <t>Publicar el contrato de la API y Postman</t>
+        </is>
+      </c>
+      <c r="E251" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F251" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-06 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G251" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H251" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I251" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J251" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K251" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L251" s="9" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="B252" s="6" t="inlineStr">
@@ -24604,48 +25244,750 @@
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
+          <t>HT-07</t>
+        </is>
+      </c>
+      <c r="D252" s="7" t="inlineStr">
+        <is>
+          <t>Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>Cargar en la base los 626 proveedores y el catálogo de insumos del cliente</t>
+        </is>
+      </c>
+      <c r="G252" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J252" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="K252" s="7" t="inlineStr">
+        <is>
+          <t>cargador idempotente ya probado</t>
+        </is>
+      </c>
+      <c r="L252" s="7" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="6" t="inlineStr">
+        <is>
+          <t>T-248</t>
+        </is>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>HT-07</t>
+        </is>
+      </c>
+      <c r="D253" s="7" t="inlineStr">
+        <is>
+          <t>Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="E253" s="6" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>Crear la obra Multifamiliar Flores con su relación de insumos del S10 en la base de pruebas</t>
+        </is>
+      </c>
+      <c r="G253" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H253" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J253" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="K253" s="7" t="inlineStr"/>
+      <c r="L253" s="7" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="8" t="inlineStr">
+        <is>
+          <t>T-249</t>
+        </is>
+      </c>
+      <c r="C254" s="8" t="inlineStr">
+        <is>
+          <t>HT-07</t>
+        </is>
+      </c>
+      <c r="D254" s="9" t="inlineStr">
+        <is>
+          <t>Cargar los datos de prueba reales</t>
+        </is>
+      </c>
+      <c r="E254" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F254" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-07 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G254" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H254" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I254" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J254" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K254" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L254" s="9" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="6" t="inlineStr">
+        <is>
+          <t>T-250</t>
+        </is>
+      </c>
+      <c r="C255" s="6" t="inlineStr">
+        <is>
+          <t>HT-08</t>
+        </is>
+      </c>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="E255" s="6" t="inlineStr">
+        <is>
+          <t>Integración</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>Exigir el token de servicio en Integraciones</t>
+        </is>
+      </c>
+      <c r="G255" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H255" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J255" s="6" t="inlineStr">
+        <is>
+          <t>25/10</t>
+        </is>
+      </c>
+      <c r="K255" s="7" t="inlineStr">
+        <is>
+          <t>X-Servicio-Token, 22/10</t>
+        </is>
+      </c>
+      <c r="L255" s="7" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="6" t="inlineStr">
+        <is>
+          <t>T-251</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>HT-08</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="E256" s="6" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="F256" s="7" t="inlineStr">
+        <is>
+          <t>Configurar el token de servicio en docker compose y enviarlo desde la API a Integraciones y Notificaciones</t>
+        </is>
+      </c>
+      <c r="G256" s="6" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H256" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I256" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J256" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="K256" s="7" t="inlineStr"/>
+      <c r="L256" s="7" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>T-252</t>
+        </is>
+      </c>
+      <c r="C257" s="8" t="inlineStr">
+        <is>
+          <t>HT-08</t>
+        </is>
+      </c>
+      <c r="D257" s="9" t="inlineStr">
+        <is>
+          <t>Autenticar a los servicios entre sí</t>
+        </is>
+      </c>
+      <c r="E257" s="8" t="inlineStr">
+        <is>
+          <t>Aceptación</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="inlineStr">
+        <is>
+          <t>Aceptar HT-08 como Product Owner y moverla a Done</t>
+        </is>
+      </c>
+      <c r="G257" s="8" t="inlineStr">
+        <is>
+          <t>Adiel</t>
+        </is>
+      </c>
+      <c r="H257" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I257" s="8" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J257" s="8" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K257" s="9" t="inlineStr">
+        <is>
+          <t>mueve la historia técnica a Done</t>
+        </is>
+      </c>
+      <c r="L257" s="9" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="6" t="inlineStr">
+        <is>
+          <t>T-253</t>
+        </is>
+      </c>
+      <c r="C258" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D252" s="7" t="inlineStr">
+      <c r="D258" s="7" t="inlineStr">
         <is>
           <t>Transversal</t>
         </is>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E258" s="6" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+      <c r="F258" s="7" t="inlineStr">
+        <is>
+          <t>Armar el tablero en GitHub Projects con las plantillas de DoR y DoD</t>
+        </is>
+      </c>
+      <c r="G258" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H258" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" s="6" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+      <c r="J258" s="6" t="inlineStr">
+        <is>
+          <t>23/10</t>
+        </is>
+      </c>
+      <c r="K258" s="7" t="inlineStr"/>
+      <c r="L258" s="7" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="6" t="inlineStr">
+        <is>
+          <t>T-254</t>
+        </is>
+      </c>
+      <c r="C259" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D259" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E259" s="6" t="inlineStr">
+        <is>
+          <t>Scrum</t>
+        </is>
+      </c>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>Facilitar el Daily Scrum de 15 minutos cada día, registrarlo y actualizar el burndown</t>
+        </is>
+      </c>
+      <c r="G259" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H259" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I259" s="6" t="inlineStr">
+        <is>
+          <t>Doing</t>
+        </is>
+      </c>
+      <c r="J259" s="6" t="inlineStr">
+        <is>
+          <t>27/10</t>
+        </is>
+      </c>
+      <c r="K259" s="7" t="inlineStr">
+        <is>
+          <t>hasta el 28/10</t>
+        </is>
+      </c>
+      <c r="L259" s="7" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="6" t="inlineStr">
+        <is>
+          <t>T-255</t>
+        </is>
+      </c>
+      <c r="C260" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E260" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>Simplificar los textos de cada pantalla web: título y una línea, con ayuda «?» bajo demanda</t>
+        </is>
+      </c>
+      <c r="G260" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H260" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I260" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J260" s="6" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="K260" s="7" t="inlineStr">
+        <is>
+          <t>observación de Fernando: hoy hay demasiado texto</t>
+        </is>
+      </c>
+      <c r="L260" s="7" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="6" t="inlineStr">
+        <is>
+          <t>T-256</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D261" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E261" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>Validar las pantallas con el cliente (Pool) en una sesión corta y registrar sus observaciones</t>
+        </is>
+      </c>
+      <c r="G261" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H261" s="6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I261" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J261" s="6" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="K261" s="7" t="inlineStr">
+        <is>
+          <t>que lo use quien lo va a usar</t>
+        </is>
+      </c>
+      <c r="L261" s="7" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="6" t="inlineStr">
+        <is>
+          <t>T-257</t>
+        </is>
+      </c>
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D262" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E262" s="6" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>Revisar la app con guantes y al sol: botones grandes, una acción por pantalla, contraste AA</t>
+        </is>
+      </c>
+      <c r="G262" s="6" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="H262" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J262" s="6" t="inlineStr">
+        <is>
+          <t>26/10</t>
+        </is>
+      </c>
+      <c r="K262" s="7" t="inlineStr">
+        <is>
+          <t>el almacenero trabaja en obra</t>
+        </is>
+      </c>
+      <c r="L262" s="7" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="6" t="inlineStr">
+        <is>
+          <t>T-258</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D263" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E263" s="6" t="inlineStr">
+        <is>
+          <t>Modelado UML</t>
+        </is>
+      </c>
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>Modelar los 3 diagramas de casos de uso y los 3 de secuencia (importación S10, salida sin señal, recepción y costo promedio)</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>Fernando</t>
+        </is>
+      </c>
+      <c r="H263" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I263" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J263" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="K263" s="7" t="inlineStr">
+        <is>
+          <t>en el lienzo; cubren HU-07, 35, 37, 38, 40 y 55</t>
+        </is>
+      </c>
+      <c r="L263" s="7" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="6" t="inlineStr">
+        <is>
+          <t>T-259</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E264" s="6" t="inlineStr">
+        <is>
+          <t>Modelado UML</t>
+        </is>
+      </c>
+      <c r="F264" s="7" t="inlineStr">
+        <is>
+          <t>Dibujar los diagramas de actividades del negocio y de estados</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="H264" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I264" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J264" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="K264" s="7" t="inlineStr">
+        <is>
+          <t>14 hojas: A1–A4 y E1–E3 (22/10)</t>
+        </is>
+      </c>
+      <c r="L264" s="7" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="6" t="inlineStr">
+        <is>
+          <t>T-260</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D265" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E265" s="6" t="inlineStr">
+        <is>
+          <t>Modelado UML</t>
+        </is>
+      </c>
+      <c r="F265" s="7" t="inlineStr">
+        <is>
+          <t>Dibujar la arquitectura en las cuatro vistas del C4 a partir del diagrama de microservicios</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr">
+        <is>
+          <t>Nicolás</t>
+        </is>
+      </c>
+      <c r="H265" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J265" s="6" t="inlineStr">
+        <is>
+          <t>24/10</t>
+        </is>
+      </c>
+      <c r="K265" s="7" t="inlineStr">
+        <is>
+          <t>parte de api/docs/diagrama-microservicios.png</t>
+        </is>
+      </c>
+      <c r="L265" s="7" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="6" t="inlineStr">
+        <is>
+          <t>T-261</t>
+        </is>
+      </c>
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D266" s="7" t="inlineStr">
+        <is>
+          <t>Transversal</t>
+        </is>
+      </c>
+      <c r="E266" s="6" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="F252" s="7" t="inlineStr">
+      <c r="F266" s="7" t="inlineStr">
         <is>
           <t>Preparar la demo de la Sprint Review: una compra que cruza recepción, salida y costo de punta a punta</t>
         </is>
       </c>
-      <c r="G252" s="6" t="inlineStr">
+      <c r="G266" s="6" t="inlineStr">
         <is>
           <t>Fernando</t>
         </is>
       </c>
-      <c r="H252" s="6" t="n">
+      <c r="H266" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="I252" s="6" t="inlineStr">
-        <is>
-          <t>To Do</t>
-        </is>
-      </c>
-      <c r="J252" s="6" t="inlineStr">
+      <c r="I266" s="6" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="J266" s="6" t="inlineStr">
         <is>
           <t>27/10</t>
         </is>
       </c>
-      <c r="K252" s="7" t="inlineStr"/>
-      <c r="L252" s="7" t="inlineStr"/>
+      <c r="K266" s="7" t="inlineStr"/>
+      <c r="L266" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="B5:L252"/>
-  <conditionalFormatting sqref="B6:L252">
+  <autoFilter ref="B5:L266"/>
+  <conditionalFormatting sqref="B6:L266">
     <cfRule type="expression" priority="1" dxfId="3">
       <formula>$I6="To Do"</formula>
     </cfRule>
@@ -24657,7 +25999,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I6:I252" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="I6:I266" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"To Do,Doing,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -24731,23 +26073,23 @@
         </is>
       </c>
       <c r="C5" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B5,Tablero!$I$6:$I$252,"To Do")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B5,Tablero!$I$6:$I$266,"To Do")</f>
         <v/>
       </c>
       <c r="D5" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B5,Tablero!$I$6:$I$252,"Doing")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B5,Tablero!$I$6:$I$266,"Doing")</f>
         <v/>
       </c>
       <c r="E5" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B5,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B5,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="F5" s="12">
-        <f>SUMIFS(Tablero!$H$6:$H$252,Tablero!$G$6:$G$252,B5,Tablero!$I$6:$I$252,"&lt;&gt;Done")</f>
+        <f>SUMIFS(Tablero!$H$6:$H$266,Tablero!$G$6:$G$266,B5,Tablero!$I$6:$I$266,"&lt;&gt;Done")</f>
         <v/>
       </c>
       <c r="G5" s="12">
-        <f>IF(COUNTIFS(Tablero!$G$6:$G$252,B5,Tablero!$I$6:$I$252,"Doing",Tablero!$E$6:$E$252,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
+        <f>IF(COUNTIFS(Tablero!$G$6:$G$266,B5,Tablero!$I$6:$I$266,"Doing",Tablero!$E$6:$E$266,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
         <v/>
       </c>
     </row>
@@ -24758,23 +26100,23 @@
         </is>
       </c>
       <c r="C6" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B6,Tablero!$I$6:$I$252,"To Do")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B6,Tablero!$I$6:$I$266,"To Do")</f>
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B6,Tablero!$I$6:$I$252,"Doing")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B6,Tablero!$I$6:$I$266,"Doing")</f>
         <v/>
       </c>
       <c r="E6" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B6,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B6,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>SUMIFS(Tablero!$H$6:$H$252,Tablero!$G$6:$G$252,B6,Tablero!$I$6:$I$252,"&lt;&gt;Done")</f>
+        <f>SUMIFS(Tablero!$H$6:$H$266,Tablero!$G$6:$G$266,B6,Tablero!$I$6:$I$266,"&lt;&gt;Done")</f>
         <v/>
       </c>
       <c r="G6" s="12">
-        <f>IF(COUNTIFS(Tablero!$G$6:$G$252,B6,Tablero!$I$6:$I$252,"Doing",Tablero!$E$6:$E$252,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
+        <f>IF(COUNTIFS(Tablero!$G$6:$G$266,B6,Tablero!$I$6:$I$266,"Doing",Tablero!$E$6:$E$266,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
         <v/>
       </c>
     </row>
@@ -24785,23 +26127,23 @@
         </is>
       </c>
       <c r="C7" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B7,Tablero!$I$6:$I$252,"To Do")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B7,Tablero!$I$6:$I$266,"To Do")</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B7,Tablero!$I$6:$I$252,"Doing")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B7,Tablero!$I$6:$I$266,"Doing")</f>
         <v/>
       </c>
       <c r="E7" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B7,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B7,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>SUMIFS(Tablero!$H$6:$H$252,Tablero!$G$6:$G$252,B7,Tablero!$I$6:$I$252,"&lt;&gt;Done")</f>
+        <f>SUMIFS(Tablero!$H$6:$H$266,Tablero!$G$6:$G$266,B7,Tablero!$I$6:$I$266,"&lt;&gt;Done")</f>
         <v/>
       </c>
       <c r="G7" s="12">
-        <f>IF(COUNTIFS(Tablero!$G$6:$G$252,B7,Tablero!$I$6:$I$252,"Doing",Tablero!$E$6:$E$252,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
+        <f>IF(COUNTIFS(Tablero!$G$6:$G$266,B7,Tablero!$I$6:$I$266,"Doing",Tablero!$E$6:$E$266,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
         <v/>
       </c>
     </row>
@@ -24812,23 +26154,23 @@
         </is>
       </c>
       <c r="C8" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B8,Tablero!$I$6:$I$252,"To Do")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B8,Tablero!$I$6:$I$266,"To Do")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B8,Tablero!$I$6:$I$252,"Doing")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B8,Tablero!$I$6:$I$266,"Doing")</f>
         <v/>
       </c>
       <c r="E8" s="12">
-        <f>COUNTIFS(Tablero!$G$6:$G$252,B8,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$G$6:$G$266,B8,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>SUMIFS(Tablero!$H$6:$H$252,Tablero!$G$6:$G$252,B8,Tablero!$I$6:$I$252,"&lt;&gt;Done")</f>
+        <f>SUMIFS(Tablero!$H$6:$H$266,Tablero!$G$6:$G$266,B8,Tablero!$I$6:$I$266,"&lt;&gt;Done")</f>
         <v/>
       </c>
       <c r="G8" s="12">
-        <f>IF(COUNTIFS(Tablero!$G$6:$G$252,B8,Tablero!$I$6:$I$252,"Doing",Tablero!$E$6:$E$252,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
+        <f>IF(COUNTIFS(Tablero!$G$6:$G$266,B8,Tablero!$I$6:$I$266,"Doing",Tablero!$E$6:$E$266,"&lt;&gt;Scrum")&lt;=2,"ok","demasiado en curso")</f>
         <v/>
       </c>
     </row>
@@ -24907,11 +26249,11 @@
         <v>3</v>
       </c>
       <c r="E13" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B13)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B13)</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B13,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B13,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G13" s="14">
@@ -24919,7 +26261,7 @@
         <v/>
       </c>
       <c r="H13" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B13,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F13&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B13,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F13&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -24938,11 +26280,11 @@
         <v>3</v>
       </c>
       <c r="E14" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B14)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B14)</f>
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B14,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B14,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G14" s="14">
@@ -24950,7 +26292,7 @@
         <v/>
       </c>
       <c r="H14" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B14,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F14&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B14,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F14&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -24969,11 +26311,11 @@
         <v>8</v>
       </c>
       <c r="E15" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B15)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B15)</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B15,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B15,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G15" s="14">
@@ -24981,7 +26323,7 @@
         <v/>
       </c>
       <c r="H15" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B15,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F15&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B15,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F15&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25000,11 +26342,11 @@
         <v>5</v>
       </c>
       <c r="E16" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B16)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B16)</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B16,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B16,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G16" s="14">
@@ -25012,7 +26354,7 @@
         <v/>
       </c>
       <c r="H16" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B16,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F16&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B16,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F16&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25031,11 +26373,11 @@
         <v>5</v>
       </c>
       <c r="E17" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B17)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B17)</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B17,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B17,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G17" s="14">
@@ -25043,7 +26385,7 @@
         <v/>
       </c>
       <c r="H17" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B17,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F17&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B17,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F17&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25062,11 +26404,11 @@
         <v>5</v>
       </c>
       <c r="E18" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B18)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B18)</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B18,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B18,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G18" s="14">
@@ -25074,7 +26416,7 @@
         <v/>
       </c>
       <c r="H18" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B18,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F18&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B18,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F18&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25093,11 +26435,11 @@
         <v>3</v>
       </c>
       <c r="E19" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B19)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B19)</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B19,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B19,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G19" s="14">
@@ -25105,7 +26447,7 @@
         <v/>
       </c>
       <c r="H19" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B19,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F19&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B19,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F19&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25124,11 +26466,11 @@
         <v>5</v>
       </c>
       <c r="E20" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B20)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B20)</f>
         <v/>
       </c>
       <c r="F20" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B20,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B20,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G20" s="14">
@@ -25136,7 +26478,7 @@
         <v/>
       </c>
       <c r="H20" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B20,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F20&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B20,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F20&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25155,11 +26497,11 @@
         <v>8</v>
       </c>
       <c r="E21" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B21)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B21)</f>
         <v/>
       </c>
       <c r="F21" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B21,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B21,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G21" s="14">
@@ -25167,7 +26509,7 @@
         <v/>
       </c>
       <c r="H21" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B21,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F21&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B21,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F21&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25186,11 +26528,11 @@
         <v>3</v>
       </c>
       <c r="E22" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B22)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B22)</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B22,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B22,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G22" s="14">
@@ -25198,7 +26540,7 @@
         <v/>
       </c>
       <c r="H22" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B22,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F22&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B22,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F22&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25217,11 +26559,11 @@
         <v>5</v>
       </c>
       <c r="E23" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B23)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B23)</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B23,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B23,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G23" s="14">
@@ -25229,7 +26571,7 @@
         <v/>
       </c>
       <c r="H23" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B23,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F23&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B23,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F23&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25248,11 +26590,11 @@
         <v>5</v>
       </c>
       <c r="E24" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B24)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B24)</f>
         <v/>
       </c>
       <c r="F24" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B24,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B24,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G24" s="14">
@@ -25260,7 +26602,7 @@
         <v/>
       </c>
       <c r="H24" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B24,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F24&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B24,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F24&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25279,11 +26621,11 @@
         <v>3</v>
       </c>
       <c r="E25" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B25)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B25)</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B25,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B25,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G25" s="14">
@@ -25291,7 +26633,7 @@
         <v/>
       </c>
       <c r="H25" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B25,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F25&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B25,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F25&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25310,11 +26652,11 @@
         <v>5</v>
       </c>
       <c r="E26" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B26)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B26)</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B26,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B26,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G26" s="14">
@@ -25322,7 +26664,7 @@
         <v/>
       </c>
       <c r="H26" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B26,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F26&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B26,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F26&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25341,11 +26683,11 @@
         <v>5</v>
       </c>
       <c r="E27" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B27)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B27)</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B27,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B27,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G27" s="14">
@@ -25353,7 +26695,7 @@
         <v/>
       </c>
       <c r="H27" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B27,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F27&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B27,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F27&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25372,11 +26714,11 @@
         <v>5</v>
       </c>
       <c r="E28" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B28)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B28)</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B28,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B28,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G28" s="14">
@@ -25384,7 +26726,7 @@
         <v/>
       </c>
       <c r="H28" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B28,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F28&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B28,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F28&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25403,11 +26745,11 @@
         <v>3</v>
       </c>
       <c r="E29" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B29)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B29)</f>
         <v/>
       </c>
       <c r="F29" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B29,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B29,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G29" s="14">
@@ -25415,7 +26757,7 @@
         <v/>
       </c>
       <c r="H29" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B29,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F29&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B29,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F29&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25434,11 +26776,11 @@
         <v>3</v>
       </c>
       <c r="E30" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B30)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B30)</f>
         <v/>
       </c>
       <c r="F30" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B30,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B30,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G30" s="14">
@@ -25446,7 +26788,7 @@
         <v/>
       </c>
       <c r="H30" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B30,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F30&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B30,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F30&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25465,11 +26807,11 @@
         <v>8</v>
       </c>
       <c r="E31" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B31)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B31)</f>
         <v/>
       </c>
       <c r="F31" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B31,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B31,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G31" s="14">
@@ -25477,7 +26819,7 @@
         <v/>
       </c>
       <c r="H31" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B31,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F31&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B31,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F31&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25496,11 +26838,11 @@
         <v>8</v>
       </c>
       <c r="E32" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B32)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B32)</f>
         <v/>
       </c>
       <c r="F32" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B32,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B32,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G32" s="14">
@@ -25508,7 +26850,7 @@
         <v/>
       </c>
       <c r="H32" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B32,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F32&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B32,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F32&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25527,11 +26869,11 @@
         <v>8</v>
       </c>
       <c r="E33" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B33)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B33)</f>
         <v/>
       </c>
       <c r="F33" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B33,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B33,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G33" s="14">
@@ -25539,7 +26881,7 @@
         <v/>
       </c>
       <c r="H33" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B33,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F33&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B33,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F33&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25558,11 +26900,11 @@
         <v>5</v>
       </c>
       <c r="E34" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B34)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B34)</f>
         <v/>
       </c>
       <c r="F34" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B34,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B34,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G34" s="14">
@@ -25570,7 +26912,7 @@
         <v/>
       </c>
       <c r="H34" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B34,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F34&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B34,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F34&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25589,11 +26931,11 @@
         <v>8</v>
       </c>
       <c r="E35" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B35)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B35)</f>
         <v/>
       </c>
       <c r="F35" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B35,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B35,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G35" s="14">
@@ -25601,7 +26943,7 @@
         <v/>
       </c>
       <c r="H35" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B35,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F35&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B35,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F35&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25620,11 +26962,11 @@
         <v>5</v>
       </c>
       <c r="E36" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B36)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B36)</f>
         <v/>
       </c>
       <c r="F36" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B36,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B36,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G36" s="14">
@@ -25632,7 +26974,7 @@
         <v/>
       </c>
       <c r="H36" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B36,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F36&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B36,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F36&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25651,11 +26993,11 @@
         <v>5</v>
       </c>
       <c r="E37" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B37)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B37)</f>
         <v/>
       </c>
       <c r="F37" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B37,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B37,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G37" s="14">
@@ -25663,7 +27005,7 @@
         <v/>
       </c>
       <c r="H37" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B37,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F37&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B37,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F37&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25682,11 +27024,11 @@
         <v>8</v>
       </c>
       <c r="E38" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B38)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B38)</f>
         <v/>
       </c>
       <c r="F38" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B38,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B38,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G38" s="14">
@@ -25694,7 +27036,7 @@
         <v/>
       </c>
       <c r="H38" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B38,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F38&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B38,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F38&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25713,11 +27055,11 @@
         <v>8</v>
       </c>
       <c r="E39" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B39)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B39)</f>
         <v/>
       </c>
       <c r="F39" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B39,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B39,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G39" s="14">
@@ -25725,7 +27067,7 @@
         <v/>
       </c>
       <c r="H39" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B39,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F39&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B39,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F39&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25744,11 +27086,11 @@
         <v>3</v>
       </c>
       <c r="E40" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B40)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B40)</f>
         <v/>
       </c>
       <c r="F40" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B40,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B40,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G40" s="14">
@@ -25756,7 +27098,7 @@
         <v/>
       </c>
       <c r="H40" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B40,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F40&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B40,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F40&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
@@ -25775,11 +27117,11 @@
         <v>5</v>
       </c>
       <c r="E41" s="12">
-        <f>COUNTIF(Tablero!$C$6:$C$252,B41)</f>
+        <f>COUNTIF(Tablero!$C$6:$C$266,B41)</f>
         <v/>
       </c>
       <c r="F41" s="12">
-        <f>COUNTIFS(Tablero!$C$6:$C$252,B41,Tablero!$I$6:$I$252,"Done")</f>
+        <f>COUNTIFS(Tablero!$C$6:$C$266,B41,Tablero!$I$6:$I$266,"Done")</f>
         <v/>
       </c>
       <c r="G41" s="14">
@@ -25787,7 +27129,7 @@
         <v/>
       </c>
       <c r="H41" s="12">
-        <f>IF(COUNTIFS(Tablero!$C$6:$C$252,B41,Tablero!$E$6:$E$252,"Aceptación",Tablero!$I$6:$I$252,"Done")=1,"Done",IF(F41&gt;0,"Doing","To Do"))</f>
+        <f>IF(COUNTIFS(Tablero!$C$6:$C$266,B41,Tablero!$E$6:$E$266,"Aceptación",Tablero!$I$6:$I$266,"Done")=1,"Done",IF(F41&gt;0,"Doing","To Do"))</f>
         <v/>
       </c>
     </row>
